--- a/C5A.xlsx
+++ b/C5A.xlsx
@@ -1025,9 +1025,9 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.15"/>
